--- a/Analysis/duplication_rates_all_runs.xlsx
+++ b/Analysis/duplication_rates_all_runs.xlsx
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F18" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G18" t="n">
-        <v>70.6215</v>
+        <v>66.11109999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1029,10 +1029,10 @@
         <v>180</v>
       </c>
       <c r="F21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" t="n">
-        <v>67.2222</v>
+        <v>67.7778</v>
       </c>
     </row>
     <row r="22">
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G24" t="n">
-        <v>67.81610000000001</v>
+        <v>66.11109999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F27" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G27" t="n">
-        <v>66.66670000000001</v>
+        <v>67.2222</v>
       </c>
     </row>
     <row r="28">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F30" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G30" t="n">
-        <v>68.3908</v>
+        <v>67.7778</v>
       </c>
     </row>
     <row r="31">
@@ -2247,10 +2247,10 @@
         <v>180</v>
       </c>
       <c r="F63" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G63" t="n">
-        <v>61.1111</v>
+        <v>61.6667</v>
       </c>
     </row>
     <row r="64">
@@ -2334,10 +2334,10 @@
         <v>180</v>
       </c>
       <c r="F66" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G66" t="n">
-        <v>65</v>
+        <v>65.5556</v>
       </c>
     </row>
     <row r="67">
@@ -2421,10 +2421,10 @@
         <v>180</v>
       </c>
       <c r="F69" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G69" t="n">
-        <v>64.4444</v>
+        <v>63.3333</v>
       </c>
     </row>
     <row r="70">
@@ -2508,10 +2508,10 @@
         <v>180</v>
       </c>
       <c r="F72" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G72" t="n">
-        <v>64.4444</v>
+        <v>60.5556</v>
       </c>
     </row>
     <row r="73">
@@ -2595,10 +2595,10 @@
         <v>180</v>
       </c>
       <c r="F75" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G75" t="n">
-        <v>60.5556</v>
+        <v>63.8889</v>
       </c>
     </row>
     <row r="76">
@@ -3552,10 +3552,10 @@
         <v>180</v>
       </c>
       <c r="F108" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G108" t="n">
-        <v>92.2222</v>
+        <v>91.66670000000001</v>
       </c>
     </row>
     <row r="109">
@@ -3639,10 +3639,10 @@
         <v>180</v>
       </c>
       <c r="F111" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G111" t="n">
-        <v>92.2222</v>
+        <v>92.7778</v>
       </c>
     </row>
     <row r="112">
@@ -3726,10 +3726,10 @@
         <v>180</v>
       </c>
       <c r="F114" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G114" t="n">
-        <v>92.2222</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="115">
@@ -3813,10 +3813,10 @@
         <v>180</v>
       </c>
       <c r="F117" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G117" t="n">
-        <v>92.2222</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="118">
@@ -3900,10 +3900,10 @@
         <v>180</v>
       </c>
       <c r="F120" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G120" t="n">
-        <v>91.11109999999999</v>
+        <v>92.7778</v>
       </c>
     </row>
     <row r="121">
@@ -5031,10 +5031,10 @@
         <v>180</v>
       </c>
       <c r="F159" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G159" t="n">
-        <v>67.7778</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160">
@@ -5118,10 +5118,10 @@
         <v>180</v>
       </c>
       <c r="F162" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G162" t="n">
-        <v>71.11109999999999</v>
+        <v>67.2222</v>
       </c>
     </row>
     <row r="163">
@@ -5205,10 +5205,10 @@
         <v>180</v>
       </c>
       <c r="F165" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G165" t="n">
-        <v>65.5556</v>
+        <v>62.7778</v>
       </c>
     </row>
     <row r="166">
@@ -5879,16 +5879,16 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>68.1435</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528</v>
+        <v>0.8426</v>
       </c>
       <c r="G6" t="n">
-        <v>66.66670000000001</v>
+        <v>66.11109999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>70.6215</v>
+        <v>67.7778</v>
       </c>
     </row>
     <row r="7">
@@ -6167,16 +6167,16 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>63.1111</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1008</v>
+        <v>1.9484</v>
       </c>
       <c r="G15" t="n">
         <v>60.5556</v>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>65.5556</v>
       </c>
     </row>
     <row r="16">
@@ -6455,16 +6455,16 @@
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>92</v>
+        <v>92.7778</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4969</v>
+        <v>0.6804</v>
       </c>
       <c r="G24" t="n">
-        <v>91.11109999999999</v>
+        <v>91.66670000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>92.2222</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="25">
@@ -6743,16 +6743,16 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>67.44450000000001</v>
+        <v>66.5556</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2771</v>
+        <v>2.6469</v>
       </c>
       <c r="G33" t="n">
-        <v>65.5556</v>
+        <v>62.7778</v>
       </c>
       <c r="H33" t="n">
-        <v>71.11109999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
